--- a/exports/colleges/27874_institute-of-hotel-management-catering-technology-and-applied-nutrition-ihm-mumbai.xlsx
+++ b/exports/colleges/27874_institute-of-hotel-management-catering-technology-and-applied-nutrition-ihm-mumbai.xlsx
@@ -605,11 +605,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="68" customWidth="1" min="3" max="3"/>
     <col width="68" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHM</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.87 Lakhs</t>
+          <t>4.87 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 + NCHMCT JEE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NCHMCT JEE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>26 May - 20 Jun 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diploma in Hotel Management</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -764,17 +764,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Diploma</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.06 Lakhs</t>
+          <t>1.06 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 Year 6 Months</t>
+          <t>1 year 6 months</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>30 May 2025</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PG Diploma in Hotel Management</t>
+          <t>Post Graduate Diploma in Hotel Management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Post Graduate Diploma in Hotel Management</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MHM</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.13 Lakhs</t>
+          <t>3.13 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation + NCHMCT MSc JEE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NCHMCT JEE</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>30 May 2025</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,17 +940,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>BHM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B.Sc(HHA)</t>
+          <t>Bachelor of Science [B.Sc] (Hospitality and Hotel Administration)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B.Sc(HHA)</t>
+          <t>Bachelor of Science [B.Sc] (Hospitality and Hotel Administration)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 + NCHMCT JEE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NCHMCT JEE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Diploma in Hotel Management</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Diploma</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Diploma</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Diploma</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>1.06 Lakhs</t>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 Year 6 Months</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>PG Diploma in Hotel Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Post Graduate Diploma in Hotel Management</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Post Graduate Diploma in Hotel Management</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>MHM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.Sc(HA)</t>
+          <t>Master of Science [M.Sc] (Hospitality Administration)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M.Sc(HA)</t>
+          <t>Master of Science [M.Sc] (Hospitality Administration)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NCHMCT MSc JEE</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>NCHMCT JEE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
+          <t>B.Sc(HHA)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
+          <t>B.Sc(HHA)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diploma Food Production</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diploma Food Production</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diploma Food Production</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1312,22 +1312,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Diploma Bakery And Confectionery</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diploma Bakery And Confectionery</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Diploma Bakery And Confectionery</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.06 Lakhs</t>
+          <t>83,800</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diploma Food Beverage Service</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diploma Food Beverage Service</t>
+          <t>M.Sc(HA)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Diploma Food Beverage Service</t>
+          <t>M.Sc(HA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68,200</t>
+          <t>3.13 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diploma Bartending</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diploma Bartending</t>
+          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Diploma Bartending</t>
+          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47,300</t>
+          <t>4.87 Lakhs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1498,22 +1498,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Diploma Food Production</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diploma Housekeeping Executive</t>
+          <t>Diploma Food Production</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Diploma Housekeeping Executive</t>
+          <t>Diploma Food Production</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68,200</t>
+          <t>1.06 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1560,22 +1560,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PG Diploma Hotel Management</t>
+          <t>Diploma Bakery And Confectionery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PG Diploma Hotel Management</t>
+          <t>Diploma Bakery And Confectionery</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PG Diploma Hotel Management</t>
+          <t>Diploma Bakery And Confectionery</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83,800</t>
+          <t>1.06 Lakhs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1622,51 +1622,299 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Diploma Food Beverage Service</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Diploma Food Beverage Service</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Diploma Food Beverage Service</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>68,200</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>27874</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Diploma Bartending</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Diploma Bartending</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Diploma Bartending</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>47,300</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>27874</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Executive Programme</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Diploma Housekeeping Executive</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Diploma Housekeeping Executive</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>68,200</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>27874</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PG Diploma Hotel Management</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PG Diploma Hotel Management</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PG Diploma Hotel Management</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>83,800</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>27874</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>M.Sc(HA)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>M.Sc(HA) (General)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>3.13 Lakhs</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
